--- a/Employee_Reports_wi52/Venice Mendova Jadloc Q0149.xlsx
+++ b/Employee_Reports_wi52/Venice Mendova Jadloc Q0149.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-16</v>
+        <v>-24</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-13</v>
+        <v>-21</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="5" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="5" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="5" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
@@ -936,53 +936,53 @@
       <c r="K10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Bin Hoist S-Type (DFW Trainings)</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>QDFWH</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>LSME-QDF-M-011</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>29-Sep-2024</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>29-Sep-2026</t>
         </is>
       </c>
-      <c r="H11" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr"/>
+      <c r="H11" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="5" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
@@ -1362,11 +1362,11 @@
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-252</v>
+        <v>-260</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1411,11 +1411,11 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-163</v>
+        <v>-171</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1460,11 +1460,11 @@
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-160</v>
+        <v>-168</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1509,11 +1509,11 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-148</v>
+        <v>-156</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1558,11 +1558,11 @@
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-105</v>
+        <v>-113</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1595,11 +1595,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
